--- a/data/gravel/MMR Simun 2025.xlsx
+++ b/data/gravel/MMR Simun 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FE51C5-B19C-DE46-87AD-5E8D8CF67883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB6CD57-B6F7-184E-92AF-81D82FBC2533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34660" yWindow="-20600" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>L CRANK (P)</t>
+  </si>
+  <si>
+    <t>https://mmrbikes.com/cdn/shop/files/080888_SIMUN_STEELGREY_00_01_compressed.jpg?v=1737388681&amp;width=1100</t>
   </si>
 </sst>
 </file>
@@ -782,6 +785,11 @@
         <v>93</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>

--- a/data/gravel/MMR Simun 2025.xlsx
+++ b/data/gravel/MMR Simun 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB6CD57-B6F7-184E-92AF-81D82FBC2533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CD502D-77CB-904D-9754-7477267BC214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34660" yWindow="-20600" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11540" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -305,9 +305,6 @@
     <t>trail_mechanical</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>integrated</t>
   </si>
   <si>
@@ -390,6 +387,15 @@
   </si>
   <si>
     <t>https://mmrbikes.com/cdn/shop/files/080888_SIMUN_STEELGREY_00_01_compressed.jpg?v=1737388681&amp;width=1100</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Avilés, Asturias, Spain</t>
   </si>
 </sst>
 </file>
@@ -738,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -758,7 +764,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -782,12 +788,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -803,7 +809,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>78</v>
@@ -820,7 +826,7 @@
         <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2">
         <v>998</v>
@@ -840,7 +846,7 @@
         <v>86</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2">
         <v>496</v>
@@ -860,7 +866,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2">
         <v>513</v>
@@ -880,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2">
         <v>87</v>
@@ -900,7 +906,7 @@
         <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -908,7 +914,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" s="2">
         <v>440</v>
@@ -928,7 +934,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C15" s="2">
         <v>425</v>
@@ -948,7 +954,7 @@
         <v>89</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C16" s="2">
         <v>50</v>
@@ -968,7 +974,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C17" s="2">
         <v>73</v>
@@ -988,7 +994,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C18" s="2">
         <v>70.5</v>
@@ -1008,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C19" s="2">
         <v>74.5</v>
@@ -1088,7 +1094,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C23" s="2">
         <v>90</v>
@@ -1108,7 +1114,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" s="2">
         <v>170</v>
@@ -1314,19 +1320,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="G38" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1337,19 +1343,19 @@
         <v>30</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="G39" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -1499,7 +1505,7 @@
         <v>51</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -1581,7 +1587,15 @@
         <v>65</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>90</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/MMR Simun 2025.xlsx
+++ b/data/gravel/MMR Simun 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CD502D-77CB-904D-9754-7477267BC214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D001FA0F-2ECA-3640-BEB1-93FE65004603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11540" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="127">
   <si>
     <t>brand</t>
   </si>
@@ -396,6 +396,24 @@
   </si>
   <si>
     <t>Avilés, Asturias, Spain</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -744,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -1454,147 +1472,177 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>43</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B67" s="2">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B73" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B75" s="2">
-        <v>3107</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B81" s="2">
+        <v>3107</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>120</v>
       </c>
     </row>
